--- a/output/pdf_financials_xlsx/BRED.xlsx
+++ b/output/pdf_financials_xlsx/BRED.xlsx
@@ -1191,10 +1191,10 @@
         <v>0</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.111496</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.249737</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
@@ -1235,10 +1235,10 @@
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.111496</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.249737</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
@@ -1499,10 +1499,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.448996</v>
+        <v>0.3375</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.503757</v>
+        <v>0.25402</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1.13938</v>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">

--- a/output/pdf_financials_xlsx/BRED.xlsx
+++ b/output/pdf_financials_xlsx/BRED.xlsx
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.343281</v>
+        <v>0.497905</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2.180828</v>
+        <v>2.699804</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2.984147</v>
+        <v>3.81507</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4.033906</v>
+        <v>6.210882</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4.519643</v>
+        <v>7.958268</v>
       </c>
     </row>
     <row r="10">
@@ -2664,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.005076</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -10734,7 +10734,11 @@
           <t>Occupancy cost</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -13968,7 +13972,11 @@
           <t>Occupancy cost</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E259" s="5" t="n">
         <v>0.154624</v>
       </c>

--- a/output/pdf_financials_xlsx/BRED.xlsx
+++ b/output/pdf_financials_xlsx/BRED.xlsx
@@ -3506,16 +3506,16 @@
         </is>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.449047</v>
+        <v>-2.835067</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-2.993599</v>
+        <v>-3.283953</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-3.33308</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>1.15286</v>
+        <v>1.137992</v>
       </c>
     </row>
   </sheetData>
@@ -7321,7 +7321,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -10153,7 +10157,11 @@
           <t>Shares issued as finder’s fees on private placement</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
